--- a/Dev_GNC/TableData/Proto/Proto_MonsterDataTable.xlsx
+++ b/Dev_GNC/TableData/Proto/Proto_MonsterDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\Proto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\Proto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAEFDD2-CCF1-4B30-99BE-DD6B2588CE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84ECE4FA-F5F2-4EFE-B263-6E206AF705D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42480" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_Schema" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
   <si>
     <t>MessageName</t>
   </si>
@@ -112,13 +112,7 @@
     <t>시야</t>
   </si>
   <si>
-    <t>prefabPath</t>
-  </si>
-  <si>
     <t>리소스경로</t>
-  </si>
-  <si>
-    <t>projectilePath</t>
   </si>
   <si>
     <t>투사체 리소스 경로</t>
@@ -176,6 +170,18 @@
       </rPr>
       <t>경험치</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>classref:ACardGameActor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>actorLink</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>projectilePath</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -257,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -269,6 +275,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -694,11 +701,11 @@
     </row>
     <row r="12" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
+      <c r="B12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="D12" s="2">
         <v>11</v>
@@ -707,12 +714,12 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
-        <v>32</v>
+      <c r="B13" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>12</v>
@@ -724,41 +731,41 @@
         <v>9</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" s="5">
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="5">
         <v>14</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Dev_GNC/TableData/Proto/Proto_MonsterDataTable.xlsx
+++ b/Dev_GNC/TableData/Proto/Proto_MonsterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\Proto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84ECE4FA-F5F2-4EFE-B263-6E206AF705D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14DAF9A-3D8A-4F96-BA08-14E4BEF8533E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42480" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39180" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_Schema" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>Alias</t>
-  </si>
-  <si>
-    <t>name</t>
   </si>
   <si>
     <t>이름</t>
@@ -182,6 +179,10 @@
   </si>
   <si>
     <t>projectilePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>nameAlias</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -557,8 +558,8 @@
     </row>
     <row r="4" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
+      <c r="B4" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
@@ -570,13 +571,13 @@
         <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
@@ -588,13 +589,13 @@
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
@@ -606,13 +607,13 @@
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -624,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>8</v>
@@ -642,49 +643,49 @@
         <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
@@ -696,16 +697,16 @@
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="2">
         <v>11</v>
@@ -714,12 +715,12 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>12</v>
@@ -731,41 +732,41 @@
         <v>9</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="D14" s="5">
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="5">
         <v>14</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
